--- a/ecommerce-analytics-pipeline/Project1_ EDA (query results).xlsx
+++ b/ecommerce-analytics-pipeline/Project1_ EDA (query results).xlsx
@@ -1,23 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\Profesional\CV-Projects\Project 1 E-comerce\ecommerce-analytics-pipeline\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B3A64F-1A31-4211-B722-897E10ACC436}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Issue 1-2 repeated orders" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Issue 3 dates" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Issue 4-5 variants of a variabl" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="issue 6 whitespaces&amp;case" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="issue 7 null&amp;empty" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="issue 8 &quot;$&quot; will not cast" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Issue 9 orphan orders" sheetId="7" r:id="rId11"/>
+    <sheet name="Issue 1-2 repeated orders" sheetId="1" r:id="rId1"/>
+    <sheet name="Issue 3 dates" sheetId="2" r:id="rId2"/>
+    <sheet name="Issue 4-5 variants of a variabl" sheetId="3" r:id="rId3"/>
+    <sheet name="issue 6 whitespaces&amp;case" sheetId="4" r:id="rId4"/>
+    <sheet name="issue 7 null&amp;empty" sheetId="5" r:id="rId5"/>
+    <sheet name="issue 8 &quot;$&quot; will not cast" sheetId="6" r:id="rId6"/>
+    <sheet name="Issue 9 orphan orders" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
   <si>
     <t>Table Orders</t>
   </si>
@@ -94,9 +103,6 @@
     <t>usd</t>
   </si>
   <si>
-    <t>LAPTOPS</t>
-  </si>
-  <si>
     <t>USA</t>
   </si>
   <si>
@@ -226,9 +232,6 @@
     <t>[accessories]</t>
   </si>
   <si>
-    <t>[category]</t>
-  </si>
-  <si>
     <t>gaming</t>
   </si>
   <si>
@@ -262,36 +265,52 @@
     <t>order_total</t>
   </si>
   <si>
-    <t>ORD-0000150</t>
-  </si>
-  <si>
     <t>orphan_items</t>
   </si>
   <si>
     <t>orphan_payments</t>
   </si>
   <si>
-    <t>ORD-0000404</t>
-  </si>
-  <si>
-    <t>ORD-0000457</t>
+    <t>2.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Laptops </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gaming</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LAPTOPS  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Smartphones</t>
+  </si>
+  <si>
+    <t>$23.08</t>
+  </si>
+  <si>
+    <t>$1,564.14</t>
+  </si>
+  <si>
+    <t>$33.74</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -302,11 +321,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -320,54 +345,66 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>904875</xdr:colOff>
+      <xdr:colOff>517525</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6057900" cy="1685925"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image5.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image5.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
+        <a:xfrm>
+          <a:off x="517525" y="339725"/>
+          <a:ext cx="6057900" cy="1685925"/>
+        </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
@@ -386,11 +423,17 @@
     <xdr:ext cx="5410200" cy="3857625"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="Image"/>
+        <xdr:cNvPr id="3" name="image1.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -408,7 +451,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -419,11 +462,17 @@
     <xdr:ext cx="5676900" cy="1343025"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image6.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image6.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -441,7 +490,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -452,11 +501,17 @@
     <xdr:ext cx="6305550" cy="1981200"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image8.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image8.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -474,7 +529,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -485,11 +540,17 @@
     <xdr:ext cx="5895975" cy="914400"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image4.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image4.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -507,7 +568,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -518,11 +579,17 @@
     <xdr:ext cx="5095875" cy="1638300"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image3.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image3.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -540,7 +607,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -551,11 +618,17 @@
     <xdr:ext cx="4429125" cy="1323975"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image2.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image2.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -573,7 +646,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -584,11 +657,17 @@
     <xdr:ext cx="6858000" cy="1609725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image7.png" title="Image"/>
+        <xdr:cNvPr id="2" name="image7.png" title="Image">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -605,12 +684,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -800,24 +875,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="H4:K16"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="19.25"/>
-    <col customWidth="1" min="8" max="8" width="21.0"/>
-    <col customWidth="1" min="9" max="9" width="17.25"/>
-    <col customWidth="1" min="10" max="10" width="15.88"/>
-    <col customWidth="1" min="11" max="11" width="17.5"/>
+    <col min="5" max="5" width="19.26953125" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="17.26953125" customWidth="1"/>
+    <col min="10" max="10" width="15.90625" customWidth="1"/>
+    <col min="11" max="11" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
+    <row r="4" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H4" s="2" t="s">
         <v>4</v>
       </c>
@@ -831,55 +909,57 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H5" s="2">
-        <v>102532.0</v>
+        <v>109520</v>
       </c>
       <c r="I5" s="2">
-        <v>100001.0</v>
+        <v>106787</v>
       </c>
       <c r="J5" s="2">
-        <v>2531.0</v>
-      </c>
-      <c r="K5" s="2">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>2733</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H15" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I15" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="16">
+    </row>
+    <row r="16" spans="8:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H16" s="2">
-        <v>2501.0</v>
+        <v>2701</v>
       </c>
       <c r="I16" s="2">
-        <v>531.0</v>
+        <v>560</v>
       </c>
       <c r="J16" s="2">
-        <v>1970.0</v>
+        <v>2141</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="I3:L4"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="9:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="2" t="s">
         <v>2</v>
       </c>
@@ -893,36 +973,38 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="9:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I4" s="2">
-        <v>78596.0</v>
+        <v>84160</v>
       </c>
       <c r="J4" s="2">
-        <v>8712.0</v>
+        <v>9247</v>
       </c>
       <c r="K4" s="2">
-        <v>13719.0</v>
+        <v>14619</v>
       </c>
       <c r="L4" s="2">
-        <v>1504.0</v>
+        <v>1494</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="B17:I38"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="8" max="8" width="14.25"/>
+    <col min="8" max="8" width="14.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="17">
+    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
@@ -933,7 +1015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>5</v>
       </c>
@@ -953,217 +1035,219 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C20" s="2">
-        <v>50088.0</v>
+        <v>59264</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="2">
-        <v>94368.0</v>
+        <v>100921</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="I20" s="2">
-        <v>71928.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>72052</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="2">
-        <v>20456.0</v>
+        <v>24268</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="2">
-        <v>8163.0</v>
+        <v>8599</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I21" s="2">
-        <v>20585.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>20575</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="2">
-        <v>10635.0</v>
+        <v>13681</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F22" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22" s="2">
-        <v>10328.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>10122</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="2">
-        <v>4266.0</v>
+        <v>3754</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I23" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2">
-        <v>3654.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C25" s="2">
-        <v>3356.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>1556</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C28" s="2">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="2">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="2">
-        <v>1802.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1660.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C28" s="2">
-        <v>1400.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" s="2">
-        <v>1358.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30" s="2">
-        <v>851.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="2">
-        <v>763.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="2">
-        <v>718.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C33" s="2">
-        <v>715.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C34" s="2">
-        <v>339.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B35" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C35" s="2">
-        <v>301.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B36" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2">
-        <v>115.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37" s="2">
-        <v>54.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" ht="12.5" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="J4:L23"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="10" max="10" width="19.13"/>
-    <col customWidth="1" min="12" max="12" width="20.5"/>
+    <col min="10" max="10" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
+    <row r="4" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1174,325 +1258,332 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J5" s="2" t="s">
-        <v>11</v>
+        <v>82</v>
       </c>
       <c r="K5" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K6" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J7" s="2" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="K7" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J8" s="2" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="K8" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K9" s="2">
-        <v>40.0</v>
+        <v>40</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K10" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="K11" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="K12" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K13" s="2">
-        <v>37.0</v>
+        <v>37</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K14" s="2">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J16" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2">
+        <v>35</v>
+      </c>
+      <c r="L16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="L16" s="2" t="s">
+    </row>
+    <row r="17" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J17" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="L17" s="2" t="s">
+    </row>
+    <row r="18" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2">
+        <v>36</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K18" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="L18" s="2" t="s">
+    </row>
+    <row r="19" spans="10:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J19" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="J19" s="2" t="s">
+      <c r="K19" s="2">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K19" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="L19" s="2" t="s">
+    </row>
+    <row r="20" spans="10:12" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="J20" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="J20" s="2" t="s">
+      <c r="K20" s="2">
         <v>1</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1.0</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="10:12" ht="12.5" x14ac:dyDescent="0.25">
       <c r="J21" s="2" t="s">
         <v>70</v>
       </c>
       <c r="K21" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="10:12" ht="12.5" x14ac:dyDescent="0.25">
       <c r="J22" s="2" t="s">
         <v>72</v>
       </c>
       <c r="K22" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="10:12" ht="12.5" x14ac:dyDescent="0.25">
       <c r="J23" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K23" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="I3:K4"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="3">
+    <row r="3" spans="9:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4">
+    </row>
+    <row r="4" spans="9:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I4" s="2">
-        <v>3044.0</v>
+        <v>3068</v>
       </c>
       <c r="J4" s="2">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2">
-        <v>3044.0</v>
+        <v>3068</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="H2:I5"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H2" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="H3" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I3" s="3">
-        <v>100.75</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="H4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="3">
-        <v>105.88</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="H5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1138.42</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <v>1007378081</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" s="2">
+        <v>1015032704</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="8:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" s="2">
+        <v>1021103019</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="J4:K5"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="11" max="11" width="18.0"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4">
+    <row r="4" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J4" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="10:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="J5" s="2">
-        <v>257.0</v>
+        <v>207</v>
       </c>
       <c r="K5" s="2">
-        <v>113.0</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>